--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486324_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486324_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2897</v>
+        <v>4.2704</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4542</v>
+        <v>2.3425</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8354</v>
+        <v>1.9279</v>
       </c>
       <c r="G2" t="n">
         <v>0.07199999999999999</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3476</v>
+        <v>0.3284</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4951</v>
+        <v>0.3833</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1475</v>
+        <v>-0.055</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6588</v>
+        <v>3.0903</v>
       </c>
       <c r="E3" t="n">
         <v>3.0913</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4325</v>
+        <v>-0.0009</v>
       </c>
       <c r="G3" t="n">
         <v>2.911</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7073</v>
+        <v>-0.2758</v>
       </c>
       <c r="T3" t="n">
         <v>0.1286</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8359</v>
+        <v>-0.4044</v>
       </c>
       <c r="V3" t="n">
         <v>1.3252</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3887</v>
+        <v>2.5969</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1623</v>
+        <v>0.5082</v>
       </c>
       <c r="F4" t="n">
-        <v>2.551</v>
+        <v>2.0886</v>
       </c>
       <c r="G4" t="n">
         <v>0.9606</v>
@@ -766,13 +766,13 @@
         <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1676</v>
+        <v>0.3758</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3869</v>
+        <v>0.2836</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5546</v>
+        <v>0.0922</v>
       </c>
       <c r="V4" t="n">
         <v>0.3904</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7647</v>
+        <v>1.8995</v>
       </c>
       <c r="E5" t="n">
-        <v>0.448</v>
+        <v>0.3362</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3167</v>
+        <v>1.5633</v>
       </c>
       <c r="G5" t="n">
         <v>3.5458</v>
@@ -844,13 +844,13 @@
         <v>2.6101</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1764</v>
+        <v>0.3112</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3461</v>
+        <v>0.2343</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1697</v>
+        <v>0.0769</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5115</v>
+        <v>1.1858</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9221</v>
+        <v>2.5411</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4106</v>
+        <v>-1.3553</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7131</v>
+        <v>-1.1538</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0365</v>
+        <v>1.0248</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6766</v>
+        <v>-2.1786</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2546</v>
+        <v>2.5303</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2983</v>
+        <v>1.6091</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9562</v>
+        <v>0.9212</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9677</v>
+        <v>-3.6841</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3348</v>
+        <v>-0.5843</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.6328</v>
+        <v>-3.0998</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8276</v>
+        <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9195</v>
+        <v>-0.1379</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0601</v>
+        <v>0.2956</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8594000000000001</v>
+        <v>-0.4335</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.2599</v>
       </c>
       <c r="W6" t="n">
-        <v>1.695</v>
+        <v>1.8902</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8698</v>
+        <v>0.7331</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3175</v>
+        <v>1.6986</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4477</v>
+        <v>-0.9654</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1538</v>
+        <v>-1.7131</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0248</v>
+        <v>-0.0365</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1786</v>
+        <v>-1.6766</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5303</v>
+        <v>1.2546</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6091</v>
+        <v>0.2983</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9212</v>
+        <v>0.9562</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.6841</v>
+        <v>-2.9677</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5843</v>
+        <v>-0.3348</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.0998</v>
+        <v>-2.6328</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2175</v>
+        <v>1.7401</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3926</v>
+        <v>2.8276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4539</v>
+        <v>0.1412</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0721</v>
+        <v>-0.1634</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.526</v>
+        <v>0.3046</v>
       </c>
       <c r="V7" t="n">
-        <v>2.2599</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8902</v>
+        <v>1.695</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7673</v>
+        <v>0.6362</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4295</v>
+        <v>1.2059</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6622</v>
+        <v>-0.5697</v>
       </c>
       <c r="G8" t="n">
         <v>0.873</v>
@@ -1078,13 +1078,13 @@
         <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0633</v>
+        <v>-0.1944</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6201</v>
+        <v>0.3966</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6834</v>
+        <v>-0.5909</v>
       </c>
       <c r="V8" t="n">
         <v>-1.13</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3213</v>
+        <v>0.0168</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2976</v>
+        <v>1.9624</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9764</v>
+        <v>-1.9456</v>
       </c>
       <c r="G9" t="n">
         <v>1.9152</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7536</v>
+        <v>0.4491</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2402</v>
+        <v>0.9049</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4866</v>
+        <v>-0.4558</v>
       </c>
       <c r="V9" t="n">
         <v>-1.695</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3487</v>
+        <v>-0.7534</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0953</v>
+        <v>-0.6541</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2535</v>
+        <v>-0.0993</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6637</v>
@@ -1234,13 +1234,13 @@
         <v>2.8276</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4248</v>
+        <v>0.0201</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8051</v>
+        <v>0.2464</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3803</v>
+        <v>-0.2262</v>
       </c>
       <c r="V10" t="n">
         <v>1.3252</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3193</v>
+        <v>-0.7721</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5011</v>
+        <v>1.1716</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8204</v>
+        <v>-1.9437</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3641</v>
@@ -1312,13 +1312,13 @@
         <v>2.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0003</v>
+        <v>-0.453</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6044</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3959</v>
+        <v>-0.5191</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.9038</v>
+        <v>12.9035</v>
       </c>
       <c r="E12" t="n">
         <v>14.2037</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3002</v>
+        <v>-1.3001</v>
       </c>
       <c r="G12" t="n">
         <v>4.382899999999999</v>
@@ -1393,10 +1393,10 @@
         <v>0.5647</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7761</v>
+        <v>2.776</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2113</v>
+        <v>-2.2112</v>
       </c>
       <c r="V12" t="n">
         <v>3.6057</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9889</v>
+        <v>4.2786</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0166</v>
+        <v>5.9107</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0277</v>
+        <v>-1.6321</v>
       </c>
       <c r="G13" t="n">
         <v>4.4911</v>
@@ -1468,13 +1468,13 @@
         <v>2.3926</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8496</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1644</v>
+        <v>-0.2704</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6852</v>
+        <v>-0.2896</v>
       </c>
       <c r="V13" t="n">
         <v>0.5649999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7263</v>
+        <v>2.12</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7376</v>
+        <v>2.2905</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0113</v>
+        <v>-0.1705</v>
       </c>
       <c r="G14" t="n">
         <v>1.4473</v>
@@ -1546,13 +1546,13 @@
         <v>1.305</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2365</v>
+        <v>0.6303</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6682</v>
+        <v>0.2211</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5684</v>
+        <v>0.4092</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. DEBAUT</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6283</v>
+        <v>0.0069</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2713</v>
+        <v>-0.881</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.643</v>
+        <v>0.8879</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2358</v>
+        <v>-0.7403</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2979</v>
+        <v>-0.1825</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9379</v>
+        <v>-0.5578</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4435</v>
+        <v>-0.7068</v>
       </c>
       <c r="K15" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2295</v>
+        <v>-0.7068</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.6792</v>
+        <v>-0.0335</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5118</v>
+        <v>-0.1825</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1674</v>
+        <v>0.149</v>
       </c>
       <c r="P15" t="n">
-        <v>0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9576</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>2.994</v>
+        <v>0.0946</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7854</v>
+        <v>0.0433</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7913</v>
+        <v>0.0514</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1063</v>
+        <v>-0.0555</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3455</v>
+        <v>1.122</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2392</v>
+        <v>-1.1775</v>
       </c>
       <c r="G16" t="n">
         <v>-1.1389</v>
@@ -1702,13 +1702,13 @@
         <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0277</v>
+        <v>0.8658</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0911</v>
+        <v>0.8676</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0635</v>
+        <v>-0.0018</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1357</v>
+        <v>-0.3174</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9928</v>
+        <v>0.109</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8571</v>
+        <v>-0.4264</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7403</v>
+        <v>2.0026</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1825</v>
+        <v>1.0401</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5578</v>
+        <v>0.9626</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7068</v>
+        <v>3.5113</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.0434</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7068</v>
+        <v>2.4679</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0335</v>
+        <v>-1.5086</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1825</v>
+        <v>-0.0033</v>
       </c>
       <c r="O17" t="n">
-        <v>0.149</v>
+        <v>-1.5053</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2175</v>
+        <v>-2.6101</v>
       </c>
       <c r="R17" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0479</v>
+        <v>-0.8851</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.6177</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0205</v>
+        <v>-0.2674</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>L. DEBAUT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2185</v>
+        <v>-0.4528</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4443</v>
+        <v>1.0361</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-1.4889</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0026</v>
+        <v>-1.2358</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0401</v>
+        <v>-0.2979</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9626</v>
+        <v>-0.9379</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5113</v>
+        <v>1.4435</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0434</v>
+        <v>1.214</v>
       </c>
       <c r="L18" t="n">
-        <v>2.4679</v>
+        <v>0.2295</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5086</v>
+        <v>-2.6792</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0033</v>
+        <v>-1.5118</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5053</v>
+        <v>-1.1674</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.6101</v>
+        <v>-1.9576</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7862</v>
+        <v>0.913</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2824</v>
+        <v>1.5502</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5038</v>
+        <v>-0.6372</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3904</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2641</v>
+        <v>-1.6924</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7663</v>
+        <v>-0.431</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4978</v>
+        <v>-1.2614</v>
       </c>
       <c r="G19" t="n">
         <v>0.844</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7177</v>
+        <v>-0.146</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8099</v>
+        <v>-0.4747</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.3287</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5204</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8466</v>
+        <v>-2.2004</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1733</v>
+        <v>0.732</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0198</v>
+        <v>-2.9324</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1035</v>
@@ -2014,13 +2014,13 @@
         <v>1.9576</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6131</v>
+        <v>0.0331</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0649</v>
+        <v>0.4939</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5482</v>
+        <v>-0.4609</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5649999999999999</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9082</v>
+        <v>-3.8035</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1263</v>
+        <v>-2.2409</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7819</v>
+        <v>-1.5627</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7096</v>
+        <v>-3.9093</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.037</v>
+        <v>-1.6423</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6725</v>
+        <v>-2.2671</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5763</v>
+        <v>-0.6102</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2253</v>
+        <v>-0.976</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8016</v>
+        <v>0.3658</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1333</v>
+        <v>-3.2992</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2624</v>
+        <v>-0.6663</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1291</v>
+        <v>-2.6328</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.6101</v>
+        <v>-1.7401</v>
       </c>
       <c r="R21" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2364</v>
+        <v>-0.3515</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0601</v>
+        <v>0.1094</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1763</v>
+        <v>-0.4609</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6732</v>
+        <v>-3.8517</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0232</v>
+        <v>-3.1263</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.65</v>
+        <v>-0.7254</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9093</v>
+        <v>-1.7096</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6423</v>
+        <v>-1.037</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2671</v>
+        <v>-0.6725</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6102</v>
+        <v>-0.5763</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.976</v>
+        <v>0.2253</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3658</v>
+        <v>-0.8016</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.2992</v>
+        <v>-1.1333</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6663</v>
+        <v>-1.2624</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.6328</v>
+        <v>0.1291</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.7401</v>
+        <v>-2.6101</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2212</v>
+        <v>0.2929</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.0601</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5482</v>
+        <v>0.2328</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3071</v>
+        <v>-5.4451</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9098</v>
+        <v>-4.351</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3973</v>
+        <v>-1.0942</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3305</v>
@@ -2248,13 +2248,13 @@
         <v>1.305</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8238</v>
+        <v>0.0382</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3305</v>
+        <v>0.2283</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4933</v>
+        <v>-0.1902</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7602</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.9036</v>
+        <v>-11.4133</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1701999999999995</v>
+        <v>0.1700999999999988</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.0737</v>
+        <v>-11.5836</v>
       </c>
       <c r="G24" t="n">
         <v>-4.382899999999999</v>
@@ -2317,7 +2317,7 @@
         <v>-11.8734</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.3501</v>
+        <v>-4.350099999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-22.8383</v>
@@ -2326,16 +2326,16 @@
         <v>18.488</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5649000000000005</v>
+        <v>0.9253</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2113</v>
+        <v>2.2111</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.776</v>
+        <v>-1.2859</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.605799999999999</v>
+        <v>-3.6058</v>
       </c>
       <c r="W24" t="n">
         <v>4.9104</v>
